--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>167.559998</v>
+        <v>168.350006</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-0.881399</v>
+        <v>-0.414077</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1431</v>
+        <v>5.1453</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.7466</v>
+        <v>-0.704141</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52348.390625</v>
+        <v>52299.730469</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.055795</v>
+        <v>-0.037211</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8966</v>
+        <v>5.8964</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.347468</v>
+        <v>-0.350845</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>170654</v>
+        <v>171260.59375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-0.796401</v>
+        <v>-0.443779</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>433.700012</v>
+        <v>435.450012</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.447603</v>
+        <v>-0.045904</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>451</v>
+        <v>451.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>9.267111</v>
+        <v>9.388249999999999</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25870.650391</v>
+        <v>25918.525391</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.308743</v>
+        <v>-1.12611</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4125.299805</v>
+        <v>4133.700195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>2.545425</v>
+        <v>2.754239</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>78.650002</v>
+        <v>77.910004</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>7.857931</v>
+        <v>6.843123</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>73.989998</v>
+        <v>73.129997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>6.460429</v>
+        <v>5.223018</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>105.550003</v>
+        <v>105.809998</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-2.250417</v>
+        <v>-2.009637</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1187.5</v>
+        <v>1185.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>6.335348</v>
+        <v>6.156257</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7482.709961</v>
+        <v>7492.100098</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.222018</v>
+        <v>-0.096805</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>168.350006</v>
+        <v>169.800003</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-0.414077</v>
+        <v>0.443656</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1453</v>
+        <v>5.1146</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.704141</v>
+        <v>-1.296596</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52299.730469</v>
+        <v>52487.410156</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-0.037211</v>
+        <v>0.321509</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8964</v>
+        <v>5.8474</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.350845</v>
+        <v>-1.178941</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>171260.59375</v>
+        <v>172742</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-0.443779</v>
+        <v>0.417384</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>435.450012</v>
+        <v>435.079987</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.045904</v>
+        <v>-0.130841</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>451.5</v>
+        <v>451.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>9.388249999999999</v>
+        <v>9.448819</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25918.525391</v>
+        <v>26206.890625</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.12611</v>
+        <v>-0.026055</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4133.700195</v>
+        <v>4117.700195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>2.754239</v>
+        <v>2.356516</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>77.910004</v>
+        <v>76.360001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>6.843123</v>
+        <v>4.717502</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>73.129997</v>
+        <v>71.949997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>5.223018</v>
+        <v>3.525175</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>105.809998</v>
+        <v>107.760002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-2.009637</v>
+        <v>-0.203743</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1185.5</v>
+        <v>1180.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>6.156257</v>
+        <v>5.686143</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7492.100098</v>
+        <v>7543.640137</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.096805</v>
+        <v>0.590454</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>169.800003</v>
+        <v>175.009995</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.443656</v>
+        <v>3.525579</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1146</v>
+        <v>5.1075</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.296596</v>
+        <v>-1.433616</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52487.410156</v>
+        <v>52637.011719</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.321509</v>
+        <v>0.607449</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8474</v>
+        <v>5.8296</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.178941</v>
+        <v>-1.479767</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>172742</v>
+        <v>177866</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>0.417384</v>
+        <v>3.396038</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>435.079987</v>
+        <v>436.290009</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.130841</v>
+        <v>0.14691</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>451.75</v>
+        <v>438</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>9.448819</v>
+        <v>6.117505</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26206.890625</v>
+        <v>26281.609375</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-0.026055</v>
+        <v>0.258981</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4117.700195</v>
+        <v>4104.100098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>2.356516</v>
+        <v>2.018449</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>76.360001</v>
+        <v>76.010002</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>4.717502</v>
+        <v>4.237526</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>71.949997</v>
+        <v>71.410004</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>3.525175</v>
+        <v>2.748207</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>107.760002</v>
+        <v>111.080002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-0.203743</v>
+        <v>2.870901</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1180.25</v>
+        <v>1196.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>5.686143</v>
+        <v>7.141258</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7543.640137</v>
+        <v>7575.390137</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.590454</v>
+        <v>1.013824</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>6.117505</v>
+        <v>11.689885</v>
       </c>
     </row>
     <row r="429">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4104.100098</v>
+        <v>4113.700195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>2.018449</v>
+        <v>2.257086</v>
       </c>
     </row>
     <row r="551">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1196.5</v>
+        <v>1190.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>7.141258</v>
+        <v>6.626371</v>
       </c>
     </row>
     <row r="795">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1075</v>
+        <v>5.1165</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.433616</v>
+        <v>-1.259934</v>
       </c>
     </row>
     <row r="124">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8296</v>
+        <v>5.8455</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.479767</v>
+        <v>-1.211055</v>
       </c>
     </row>
     <row r="246">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>461</v>
+        <v>467.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>11.689885</v>
+        <v>13.204119</v>
       </c>
     </row>
     <row r="429">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4113.700195</v>
+        <v>4067.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>2.257086</v>
+        <v>1.118596</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>76.010002</v>
+        <v>78.879997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>4.237526</v>
+        <v>8.17334</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>71.410004</v>
+        <v>74.129997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>2.748207</v>
+        <v>6.661867</v>
       </c>
     </row>
     <row r="673">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1190.75</v>
+        <v>1196.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>6.626371</v>
+        <v>7.118872</v>
       </c>
     </row>
     <row r="795">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>175.009995</v>
+        <v>172.25</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.525579</v>
+        <v>1.892929</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1165</v>
+        <v>5.1318</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.259934</v>
+        <v>-0.964664</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52637.011719</v>
+        <v>52498.640625</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.607449</v>
+        <v>0.342974</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8455</v>
+        <v>5.8466</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.211055</v>
+        <v>-1.192464</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>177866</v>
+        <v>175739</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>3.396038</v>
+        <v>2.159582</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>436.290009</v>
+        <v>434.600006</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>0.14691</v>
+        <v>-0.241016</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>467.25</v>
+        <v>457.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>13.204119</v>
+        <v>10.841914</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26281.609375</v>
+        <v>25873.179688</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>0.258981</v>
+        <v>-1.299095</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4067.899902</v>
+        <v>4029</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>1.118596</v>
+        <v>0.151634</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>78.879997</v>
+        <v>86.900002</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>8.17334</v>
+        <v>19.1717</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>74.129997</v>
+        <v>80.510002</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>6.661867</v>
+        <v>15.84173</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>111.080002</v>
+        <v>109.199997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>2.870901</v>
+        <v>1.129833</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1196.25</v>
+        <v>1187.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>7.118872</v>
+        <v>6.335348</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7575.390137</v>
+        <v>7515.339844</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>1.013824</v>
+        <v>0.213085</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>172.25</v>
+        <v>173.600006</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.892929</v>
+        <v>2.691513</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1318</v>
+        <v>5.0745</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.964664</v>
+        <v>-2.070462</v>
       </c>
     </row>
     <row r="124">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8466</v>
+        <v>5.7922</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.192464</v>
+        <v>-2.111823</v>
       </c>
     </row>
     <row r="246">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>434.600006</v>
+        <v>432</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.241016</v>
+        <v>-0.837827</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>457.5</v>
+        <v>465</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>10.841914</v>
+        <v>12.658995</v>
       </c>
     </row>
     <row r="429">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4029</v>
+        <v>4035.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.151634</v>
+        <v>0.32315</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>86.900002</v>
+        <v>85.260002</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>19.1717</v>
+        <v>16.922661</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>80.510002</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>15.84173</v>
+        <v>14.84892</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.199997</v>
+        <v>110.400002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>1.129833</v>
+        <v>2.241154</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1187.5</v>
+        <v>1195.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>6.335348</v>
+        <v>7.051713</v>
       </c>
     </row>
     <row r="795">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>173.600006</v>
+        <v>172.649994</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.691513</v>
+        <v>2.129542</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0745</v>
+        <v>5.0804</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-2.070462</v>
+        <v>-1.956603</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52498.640625</v>
+        <v>52471</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.342974</v>
+        <v>0.290144</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.7922</v>
+        <v>5.8103</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-2.111823</v>
+        <v>-1.805937</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>175739</v>
+        <v>175690.03125</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>2.159582</v>
+        <v>2.131116</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>432</v>
+        <v>432.140015</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.837827</v>
+        <v>-0.805688</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>12.658995</v>
+        <v>13.385827</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25873.179688</v>
+        <v>26095.494141</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.299095</v>
+        <v>-0.45101</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4035.899902</v>
+        <v>4041.800049</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.32315</v>
+        <v>0.469814</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>85.260002</v>
+        <v>84.449997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>16.922661</v>
+        <v>15.811847</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>79.81999999999999</v>
+        <v>79.040001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>14.84892</v>
+        <v>13.72662</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>110.400002</v>
+        <v>109.639999</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>2.241154</v>
+        <v>1.537318</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1195.5</v>
+        <v>1195</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>7.051713</v>
+        <v>7.00694</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7515.339844</v>
+        <v>7533.77002</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.213085</v>
+        <v>0.458841</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>172.649994</v>
+        <v>172.759995</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.129542</v>
+        <v>2.194612</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0804</v>
+        <v>5.0761</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.956603</v>
+        <v>-2.039589</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52471</v>
+        <v>52658.640625</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.290144</v>
+        <v>0.6487889999999999</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8103</v>
+        <v>5.8178</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.805937</v>
+        <v>-1.679184</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>175690.03125</v>
+        <v>176011</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>2.131116</v>
+        <v>2.3177</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>432.140015</v>
+        <v>433.399994</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.805688</v>
+        <v>-0.51647</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>13.385827</v>
+        <v>14.112659</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26095.494141</v>
+        <v>26269.230469</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-0.45101</v>
+        <v>0.211758</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4041.800049</v>
+        <v>4029.300049</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.469814</v>
+        <v>0.159093</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>84.449997</v>
+        <v>84.660004</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>15.811847</v>
+        <v>16.099843</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>79.040001</v>
+        <v>79.489998</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>13.72662</v>
+        <v>14.374098</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.639999</v>
+        <v>109.690002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>1.537318</v>
+        <v>1.583626</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1195</v>
+        <v>1204.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>7.00694</v>
+        <v>7.857623</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7533.77002</v>
+        <v>7572.399902</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.458841</v>
+        <v>0.97395</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>172.759995</v>
+        <v>170.770004</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.194612</v>
+        <v>1.017451</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0761</v>
+        <v>5.1028</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-2.039589</v>
+        <v>-1.524322</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52658.640625</v>
+        <v>52552.96875</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.6487889999999999</v>
+        <v>0.446814</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8178</v>
+        <v>5.8311</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.679184</v>
+        <v>-1.454415</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>176011</v>
+        <v>173825</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>2.3177</v>
+        <v>1.046947</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>433.399994</v>
+        <v>433.040009</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.51647</v>
+        <v>-0.599101</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>471</v>
+        <v>463.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>14.112659</v>
+        <v>12.295578</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26269.230469</v>
+        <v>25881.949219</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>0.211758</v>
+        <v>-1.265641</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4029.300049</v>
+        <v>3995.699951</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.159093</v>
+        <v>-0.676128</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>84.660004</v>
+        <v>85.949997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>16.099843</v>
+        <v>17.868896</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>79.489998</v>
+        <v>80.139999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>14.374098</v>
+        <v>15.309352</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.690002</v>
+        <v>108.419998</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>1.583626</v>
+        <v>0.407478</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1204.5</v>
+        <v>1195</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>7.857623</v>
+        <v>7.00694</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7572.399902</v>
+        <v>7533.77002</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.97395</v>
+        <v>0.458841</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>170.770004</v>
+        <v>170.630005</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.017451</v>
+        <v>0.934636</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1028</v>
+        <v>5.1108</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.524322</v>
+        <v>-1.369937</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52552.96875</v>
+        <v>52146.421875</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.446814</v>
+        <v>-0.330237</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8311</v>
+        <v>5.8439</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.454415</v>
+        <v>-1.238091</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>173825</v>
+        <v>173714</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>1.046947</v>
+        <v>0.982421</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>433.040009</v>
+        <v>429.119995</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.599101</v>
+        <v>-1.498909</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>463.5</v>
+        <v>444.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>12.295578</v>
+        <v>7.752877</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25881.949219</v>
+        <v>25520.240234</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.265641</v>
+        <v>-2.645487</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>3995.699951</v>
+        <v>4012.699951</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.676128</v>
+        <v>-0.253547</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>85.949997</v>
+        <v>88.099998</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>17.868896</v>
+        <v>20.817335</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>80.139999</v>
+        <v>82.489998</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>15.309352</v>
+        <v>18.690644</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>108.419998</v>
+        <v>107.43</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>0.407478</v>
+        <v>-0.509356</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1195</v>
+        <v>1204.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>7.00694</v>
+        <v>7.857623</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7533.77002</v>
+        <v>7457.689941</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.458841</v>
+        <v>-0.555646</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>444.75</v>
+        <v>467.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>7.752877</v>
+        <v>13.264688</v>
       </c>
     </row>
     <row r="429">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4012.699951</v>
+        <v>4018.800049</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.253547</v>
+        <v>-0.101913</v>
       </c>
     </row>
     <row r="551">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>82.489998</v>
+        <v>81.779999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>18.690644</v>
+        <v>17.669063</v>
       </c>
     </row>
     <row r="673">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1204.5</v>
+        <v>1203</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>7.857623</v>
+        <v>7.723304</v>
       </c>
     </row>
     <row r="795">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1108</v>
+        <v>5.1072</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.369937</v>
+        <v>-1.439404</v>
       </c>
     </row>
     <row r="124">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8439</v>
+        <v>5.8329</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.238091</v>
+        <v>-1.423994</v>
       </c>
     </row>
     <row r="246">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>467.5</v>
+        <v>475.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>13.264688</v>
+        <v>15.142338</v>
       </c>
     </row>
     <row r="429">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4018.800049</v>
+        <v>4020</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.101913</v>
+        <v>-0.072085</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>88.099998</v>
+        <v>88.220001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>20.817335</v>
+        <v>20.981903</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>81.779999</v>
+        <v>81.400002</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>17.669063</v>
+        <v>17.122304</v>
       </c>
     </row>
     <row r="673">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1203</v>
+        <v>1220</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>7.723304</v>
+        <v>9.245578999999999</v>
       </c>
     </row>
     <row r="795">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>170.630005</v>
+        <v>170.300003</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.934636</v>
+        <v>0.739426</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1072</v>
+        <v>5.0921</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.439404</v>
+        <v>-1.73081</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52146.421875</v>
+        <v>51839.261719</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-0.330237</v>
+        <v>-0.917326</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8329</v>
+        <v>5.8157</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.423994</v>
+        <v>-1.714674</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>173714</v>
+        <v>173371</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>0.982421</v>
+        <v>0.78303</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>429.119995</v>
+        <v>426.970001</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.498909</v>
+        <v>-1.992423</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>475.25</v>
+        <v>471.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>15.142338</v>
+        <v>14.233798</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25520.240234</v>
+        <v>25508.070312</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-2.645487</v>
+        <v>-2.691912</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4020</v>
+        <v>4064.800049</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.072085</v>
+        <v>1.041541</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>88.220001</v>
+        <v>90.400002</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>20.981903</v>
+        <v>23.971481</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>81.400002</v>
+        <v>83.620003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>17.122304</v>
+        <v>20.316551</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>107.43</v>
+        <v>106.230003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-0.509356</v>
+        <v>-1.62067</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1220</v>
+        <v>1226.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>9.245578999999999</v>
+        <v>9.827624999999999</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7457.689941</v>
+        <v>7443.279785</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.555646</v>
+        <v>-0.747798</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>170.300003</v>
+        <v>170.339996</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.739426</v>
+        <v>0.763084</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0921</v>
+        <v>5.072</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.73081</v>
+        <v>-2.118709</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51839.261719</v>
+        <v>52224.640625</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-0.917326</v>
+        <v>-0.180734</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8157</v>
+        <v>5.7838</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.714674</v>
+        <v>-2.253782</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>173371</v>
+        <v>173326</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>0.78303</v>
+        <v>0.756871</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>426.970001</v>
+        <v>430.109985</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.992423</v>
+        <v>-1.271665</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>471.5</v>
+        <v>481</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>14.233798</v>
+        <v>16.535433</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25508.070312</v>
+        <v>25837.210938</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-2.691912</v>
+        <v>-1.436308</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4064.800049</v>
+        <v>4122.799805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>1.041541</v>
+        <v>2.483281</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>90.400002</v>
+        <v>84.800003</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>23.971481</v>
+        <v>16.291834</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>83.620003</v>
+        <v>87.129997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>20.316551</v>
+        <v>25.366903</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>106.230003</v>
+        <v>105.949997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-1.62067</v>
+        <v>-1.879984</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1226.5</v>
+        <v>1227</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>9.827624999999999</v>
+        <v>9.872398</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7443.279785</v>
+        <v>7509.200195</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.747798</v>
+        <v>0.131216</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>170.339996</v>
+        <v>174.699997</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.763084</v>
+        <v>3.342203</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.072</v>
+        <v>5.0572</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-2.118709</v>
+        <v>-2.404326</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52224.640625</v>
+        <v>52218.578125</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-0.180734</v>
+        <v>-0.192322</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.7838</v>
+        <v>5.7601</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-2.253782</v>
+        <v>-2.654316</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>173326</v>
+        <v>177548</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>0.756871</v>
+        <v>3.21118</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>430.109985</v>
+        <v>428.859985</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.271665</v>
+        <v>-1.558593</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>481</v>
+        <v>488.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>16.535433</v>
+        <v>18.413083</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25837.210938</v>
+        <v>25690.900391</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.436308</v>
+        <v>-1.994453</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4122.799805</v>
+        <v>4077.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>2.483281</v>
+        <v>1.367173</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>84.800003</v>
+        <v>93.30999799999999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>16.291834</v>
+        <v>27.96215</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>87.129997</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>25.366903</v>
+        <v>31.035971</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>105.949997</v>
+        <v>107.5</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-1.879984</v>
+        <v>-0.44453</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1227</v>
+        <v>1244</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>9.872398</v>
+        <v>11.394672</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7509.200195</v>
+        <v>7498.959961</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>0.131216</v>
+        <v>-0.005332</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>174.699997</v>
+        <v>173.449997</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.342203</v>
+        <v>2.602777</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0572</v>
+        <v>5.0821</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-2.404326</v>
+        <v>-1.923798</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52218.578125</v>
+        <v>51711.648438</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-0.192322</v>
+        <v>-1.161239</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.7601</v>
+        <v>5.7826</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-2.654316</v>
+        <v>-2.274066</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>177548</v>
+        <v>176724</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>3.21118</v>
+        <v>2.732177</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>428.859985</v>
+        <v>425.519989</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.558593</v>
+        <v>-2.325262</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>488.75</v>
+        <v>487</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>18.413083</v>
+        <v>17.989098</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25690.900391</v>
+        <v>25137.689453</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-1.994453</v>
+        <v>-4.10484</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4077.899902</v>
+        <v>4062.100098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>1.367173</v>
+        <v>0.974426</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>93.30999799999999</v>
+        <v>92</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>27.96215</v>
+        <v>26.165664</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>91.06999999999999</v>
+        <v>89.879997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>31.035971</v>
+        <v>29.323737</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>107.5</v>
+        <v>106.18</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-0.44453</v>
+        <v>-1.666978</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1244</v>
+        <v>1247.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>11.394672</v>
+        <v>11.708081</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7498.959961</v>
+        <v>7408.299805</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.005332</v>
+        <v>-1.214238</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>173.449997</v>
+        <v>170.949997</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.602777</v>
+        <v>1.123924</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0821</v>
+        <v>5.0751</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.923798</v>
+        <v>-2.058886</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51711.648438</v>
+        <v>51947.25</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-1.161239</v>
+        <v>-0.710923</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.7826</v>
+        <v>5.7816</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-2.274066</v>
+        <v>-2.290964</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>176724</v>
+        <v>174042</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>2.732177</v>
+        <v>1.173092</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>425.519989</v>
+        <v>425.049988</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-2.325262</v>
+        <v>-2.433147</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>487</v>
+        <v>464.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>17.989098</v>
+        <v>12.477286</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25137.689453</v>
+        <v>24975.820312</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-4.10484</v>
+        <v>-4.722338</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4062.100098</v>
+        <v>4067.600098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.974426</v>
+        <v>1.111144</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>92</v>
+        <v>96.779999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>26.165664</v>
+        <v>32.720792</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>89.879997</v>
+        <v>89.30999799999999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>29.323737</v>
+        <v>28.503594</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>106.18</v>
+        <v>105.050003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-1.666978</v>
+        <v>-2.713466</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1247.5</v>
+        <v>1248</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>11.708081</v>
+        <v>11.752854</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7408.299805</v>
+        <v>7411.97998</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-1.214238</v>
+        <v>-1.165165</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51947.25</v>
+        <v>51711.648438</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-0.710923</v>
+        <v>-1.161239</v>
       </c>
     </row>
     <row r="185">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>174042</v>
+        <v>176724</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>1.173092</v>
+        <v>2.732177</v>
       </c>
     </row>
     <row r="307">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>464.25</v>
+        <v>487.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>12.477286</v>
+        <v>18.049667</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>24975.820312</v>
+        <v>25137.689453</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-4.722338</v>
+        <v>-4.10484</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4067.600098</v>
+        <v>4070.800049</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>1.111144</v>
+        <v>1.190687</v>
       </c>
     </row>
     <row r="551">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1248</v>
+        <v>1253.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>11.752854</v>
+        <v>12.245355</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7411.97998</v>
+        <v>7408.299805</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-1.165165</v>
+        <v>-1.214238</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0751</v>
+        <v>5.0846</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-2.058886</v>
+        <v>-1.875551</v>
       </c>
     </row>
     <row r="124">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.7816</v>
+        <v>5.7877</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-2.290964</v>
+        <v>-2.187871</v>
       </c>
     </row>
     <row r="246">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>487.25</v>
+        <v>473.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>18.049667</v>
+        <v>14.778922</v>
       </c>
     </row>
     <row r="429">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4070.800049</v>
+        <v>4089.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>1.190687</v>
+        <v>1.665465</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>96.779999</v>
+        <v>90.550003</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>32.720792</v>
+        <v>24.177188</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>89.30999799999999</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>28.503594</v>
+        <v>20.76259</v>
       </c>
     </row>
     <row r="673">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1253.5</v>
+        <v>1220.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>12.245355</v>
+        <v>9.267965</v>
       </c>
     </row>
     <row r="795">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>170.949997</v>
+        <v>172.75</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.123924</v>
+        <v>2.1887</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0846</v>
+        <v>5.1097</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.875551</v>
+        <v>-1.391157</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>51711.648438</v>
+        <v>52210.078125</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-1.161239</v>
+        <v>-0.208568</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.7877</v>
+        <v>5.8091</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-2.187871</v>
+        <v>-1.826212</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>176724</v>
+        <v>175335</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>2.732177</v>
+        <v>1.924731</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>425.049988</v>
+        <v>426.859985</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-2.433147</v>
+        <v>-2.017677</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>473.75</v>
+        <v>475.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>14.778922</v>
+        <v>15.263477</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25137.689453</v>
+        <v>24932.080078</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-4.10484</v>
+        <v>-4.889198</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4089.899902</v>
+        <v>4026.600098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>1.665465</v>
+        <v>0.091978</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>90.550003</v>
+        <v>87.160004</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>24.177188</v>
+        <v>19.528258</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>83.93000000000001</v>
+        <v>81.860001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>20.76259</v>
+        <v>17.784174</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>105.050003</v>
+        <v>106.699997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-2.713466</v>
+        <v>-1.185411</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1220.25</v>
+        <v>1208.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>9.267965</v>
+        <v>8.215805</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7408.299805</v>
+        <v>7413.180176</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-1.214238</v>
+        <v>-1.149161</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>172.75</v>
+        <v>173.740005</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.1887</v>
+        <v>2.774329</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1097</v>
+        <v>5.1259</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.391157</v>
+        <v>-1.078532</v>
       </c>
     </row>
     <row r="124">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8091</v>
+        <v>5.8325</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.826212</v>
+        <v>-1.430755</v>
       </c>
     </row>
     <row r="246">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>426.859985</v>
+        <v>428.609985</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-2.017677</v>
+        <v>-1.615978</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>475.75</v>
+        <v>478.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>15.263477</v>
+        <v>15.92974</v>
       </c>
     </row>
     <row r="429">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4026.600098</v>
+        <v>4092.399902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.091978</v>
+        <v>1.727609</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>87.160004</v>
+        <v>87.91999800000001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>19.528258</v>
+        <v>20.570489</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>81.860001</v>
+        <v>82.660004</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>17.784174</v>
+        <v>18.935257</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>106.699997</v>
+        <v>107.169998</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-1.185411</v>
+        <v>-0.750144</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1208.5</v>
+        <v>1207.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>8.215805</v>
+        <v>8.148645999999999</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7413.180176</v>
+        <v>7428.779785</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-1.149161</v>
+        <v>-0.941148</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>173.740005</v>
+        <v>170.550003</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.774329</v>
+        <v>0.887311</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1259</v>
+        <v>5.099</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.078532</v>
+        <v>-1.597654</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52210.078125</v>
+        <v>51594.140625</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-0.208568</v>
+        <v>-1.385837</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8325</v>
+        <v>5.8475</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-1.430755</v>
+        <v>-1.177257</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>175335</v>
+        <v>173885</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>1.924731</v>
+        <v>1.081826</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>428.609985</v>
+        <v>421.559998</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.615978</v>
+        <v>-3.234247</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>478.5</v>
+        <v>473.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>15.92974</v>
+        <v>14.718353</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>24932.080078</v>
+        <v>24442.939453</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-4.889198</v>
+        <v>-6.755169</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4092.399902</v>
+        <v>4136.799805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>1.727609</v>
+        <v>2.831289</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>87.91999800000001</v>
+        <v>89.889999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>20.570489</v>
+        <v>23.272081</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>82.660004</v>
+        <v>83.41999800000001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>18.935257</v>
+        <v>20.028774</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>107.169998</v>
+        <v>105.099998</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-0.750144</v>
+        <v>-2.667165</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1207.75</v>
+        <v>1193.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>8.148645999999999</v>
+        <v>6.850235</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7428.779785</v>
+        <v>7316.149902</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.941148</v>
+        <v>-2.443008</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -28233,7 +28233,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>440.75</v>
+        <v>464</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>6.783767</v>
+        <v>12.416717</v>
       </c>
     </row>
     <row r="423">
@@ -36149,7 +36149,7 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>4049.100098</v>
+        <v>4107</v>
       </c>
       <c r="I542" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         </is>
       </c>
       <c r="N542" t="n">
-        <v>0.651276</v>
+        <v>2.090534</v>
       </c>
     </row>
     <row r="543">
@@ -51981,7 +51981,7 @@
         </is>
       </c>
       <c r="H782" t="n">
-        <v>1172</v>
+        <v>1187.5</v>
       </c>
       <c r="I782" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         </is>
       </c>
       <c r="N782" t="n">
-        <v>4.947392</v>
+        <v>6.335348</v>
       </c>
     </row>
     <row r="783">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>174.899994</v>
+        <v>174.699997</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-0.06857000000000001</v>
+        <v>-0.18284</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1397</v>
+        <v>5.1165</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1.213047</v>
+        <v>0.756182</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>54085.878906</v>
+        <v>54349.121094</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>3.050103</v>
+        <v>3.55166</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9358</v>
+        <v>5.9151</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1.502188</v>
+        <v>1.148218</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>177895</v>
+        <v>177726</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-0.058427</v>
+        <v>-0.153372</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>435.829987</v>
+        <v>446.51001</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>1.736729</v>
+        <v>4.229789</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>459.25</v>
+        <v>460.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>4.197391</v>
+        <v>4.480998</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26584.990234</v>
+        <v>26363.439453</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>4.773184</v>
+        <v>3.900038</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4246.5</v>
+        <v>4312.799805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>4.875155</v>
+        <v>6.512551</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>80.279999</v>
+        <v>80.55999799999999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-10.918779</v>
+        <v>-10.608084</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>76.19000200000001</v>
+        <v>76.129997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-10.015349</v>
+        <v>-10.086218</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>108.379997</v>
+        <v>107.790001</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>1.05361</v>
+        <v>0.503497</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1167.75</v>
+        <v>1174</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-0.362628</v>
+        <v>0.170648</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7736.52002</v>
+        <v>7723.549805</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>3.295181</v>
+        <v>3.122007</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>174.699997</v>
+        <v>172.039993</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-0.18284</v>
+        <v>-1.702669</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1165</v>
+        <v>5.1014</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.756182</v>
+        <v>0.458827</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>54349.121094</v>
+        <v>53885.101562</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>3.55166</v>
+        <v>2.667561</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9151</v>
+        <v>5.8811</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1.148218</v>
+        <v>0.566819</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>177726</v>
+        <v>175546</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-0.153372</v>
+        <v>-1.378098</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>446.51001</v>
+        <v>443.950012</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>4.229789</v>
+        <v>3.632204</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>460.5</v>
+        <v>465.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>4.480998</v>
+        <v>5.558707</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26363.439453</v>
+        <v>26348.349609</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>3.900038</v>
+        <v>3.840568</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4312.799805</v>
+        <v>4375.799805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>6.512551</v>
+        <v>8.068452000000001</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>80.55999799999999</v>
+        <v>81.839996</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-10.608084</v>
+        <v>-9.187756</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>76.129997</v>
+        <v>76.879997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-10.086218</v>
+        <v>-9.200426</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>107.790001</v>
+        <v>105.910004</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>0.503497</v>
+        <v>-1.249414</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1174</v>
+        <v>1182.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>0.170648</v>
+        <v>0.874573</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7723.549805</v>
+        <v>7709.959961</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>3.122007</v>
+        <v>2.94056</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>172.039993</v>
+        <v>169.369995</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-1.702669</v>
+        <v>-3.228208</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1014</v>
+        <v>5.0842</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.458827</v>
+        <v>0.120118</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53885.101562</v>
+        <v>54036.929688</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.667561</v>
+        <v>2.95684</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8811</v>
+        <v>5.8734</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0.566819</v>
+        <v>0.43515</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>175546</v>
+        <v>172513</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-1.378098</v>
+        <v>-3.08204</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>443.950012</v>
+        <v>444.350006</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>3.632204</v>
+        <v>3.725575</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>465.25</v>
+        <v>439</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>5.558707</v>
+        <v>-0.39705</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26348.349609</v>
+        <v>26690.619141</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>3.840568</v>
+        <v>5.189475</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4375.799805</v>
+        <v>4340.700195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>8.068452000000001</v>
+        <v>7.201603</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>81.839996</v>
+        <v>83.550003</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-9.187756</v>
+        <v>-7.290279</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>76.879997</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-9.200426</v>
+        <v>-7.66505</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>105.910004</v>
+        <v>104.699997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-1.249414</v>
+        <v>-2.377625</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1182.25</v>
+        <v>1156.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>0.874573</v>
+        <v>-1.322526</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7709.959961</v>
+        <v>7757.640137</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.94056</v>
+        <v>3.577169</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>439</v>
+        <v>461.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-0.39705</v>
+        <v>4.707884</v>
       </c>
     </row>
     <row r="429">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4340.700195</v>
+        <v>4399.700195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>7.201603</v>
+        <v>8.658716</v>
       </c>
     </row>
     <row r="551">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1156.5</v>
+        <v>1176.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>-1.322526</v>
+        <v>0.362628</v>
       </c>
     </row>
     <row r="795">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0842</v>
+        <v>5.0848</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.120118</v>
+        <v>0.13193</v>
       </c>
     </row>
     <row r="124">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8734</v>
+        <v>5.8753</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0.43515</v>
+        <v>0.467635</v>
       </c>
     </row>
     <row r="246">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>461.5</v>
+        <v>463.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>4.707884</v>
+        <v>5.218378</v>
       </c>
     </row>
     <row r="429">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4399.700195</v>
+        <v>4395.700195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>8.658716</v>
+        <v>8.559929</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>83.550003</v>
+        <v>84.949997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-7.290279</v>
+        <v>-5.736802</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>78.18000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-7.66505</v>
+        <v>-6.106057</v>
       </c>
     </row>
     <row r="673">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1176.25</v>
+        <v>1183.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>0.362628</v>
+        <v>0.959898</v>
       </c>
     </row>
     <row r="795">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>169.369995</v>
+        <v>169.270004</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-3.228208</v>
+        <v>-3.285339</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.0848</v>
+        <v>5.1133</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.13193</v>
+        <v>0.6931659999999999</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>54036.929688</v>
+        <v>53975.980469</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.95684</v>
+        <v>2.840713</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8753</v>
+        <v>5.8987</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0.467635</v>
+        <v>0.867781</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>172513</v>
+        <v>172180</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-3.08204</v>
+        <v>-3.269119</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>444.350006</v>
+        <v>446.850006</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>3.725575</v>
+        <v>4.309155</v>
       </c>
     </row>
     <row r="368">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26690.619141</v>
+        <v>26605.359375</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>5.189475</v>
+        <v>4.85346</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4395.700195</v>
+        <v>4436.600098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>8.559929</v>
+        <v>9.570028000000001</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>84.949997</v>
+        <v>89.19000200000001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-5.736802</v>
+        <v>-1.031958</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>79.5</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-6.106057</v>
+        <v>-1.169243</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>104.699997</v>
+        <v>103.519997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-2.377625</v>
+        <v>-3.477859</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1183.25</v>
+        <v>1180.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>0.959898</v>
+        <v>0.746587</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7757.640137</v>
+        <v>7753.109863</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>3.577169</v>
+        <v>3.516682</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1133</v>
+        <v>5.1716</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.6931659999999999</v>
+        <v>1.841233</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53975.980469</v>
+        <v>53791.851562</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.840713</v>
+        <v>2.489891</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.8987</v>
+        <v>5.9654</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0.867781</v>
+        <v>2.00835</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>172180</v>
+        <v>167875</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-3.269119</v>
+        <v>-5.687672</v>
       </c>
     </row>
     <row r="307">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>463.75</v>
+        <v>465.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>5.218378</v>
+        <v>5.67215</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26605.359375</v>
+        <v>26445.449219</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>4.85346</v>
+        <v>4.223244</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4436.600098</v>
+        <v>4469</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>9.570028000000001</v>
+        <v>10.370203</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>89.19000200000001</v>
+        <v>89.220001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-1.031958</v>
+        <v>-0.9986699999999999</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>83.68000000000001</v>
+        <v>83.519997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-1.169243</v>
+        <v>-1.358216</v>
       </c>
     </row>
     <row r="673">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1180.75</v>
+        <v>1175.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>0.746587</v>
+        <v>0.277304</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7753.109863</v>
+        <v>7728.200195</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>3.516682</v>
+        <v>3.184097</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>169.270004</v>
+        <v>165.050003</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-3.285339</v>
+        <v>-5.696492</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1716</v>
+        <v>5.1612</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1.841233</v>
+        <v>1.636436</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53791.851562</v>
+        <v>53770.269531</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.489891</v>
+        <v>2.448771</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9654</v>
+        <v>5.9514</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2.00835</v>
+        <v>1.768943</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>167875</v>
+        <v>167491</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-5.687672</v>
+        <v>-5.903404</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>446.850006</v>
+        <v>450.350006</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>4.309155</v>
+        <v>5.126168</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>465.75</v>
+        <v>478.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>5.67215</v>
+        <v>8.508224999999999</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26445.449219</v>
+        <v>26588.490234</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>4.223244</v>
+        <v>4.786978</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4469</v>
+        <v>4450.399902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>10.370203</v>
+        <v>9.910838999999999</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>89.220001</v>
+        <v>87.220001</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-0.9986699999999999</v>
+        <v>-3.217933</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>83.519997</v>
+        <v>81.459999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-1.358216</v>
+        <v>-3.791188</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>103.519997</v>
+        <v>101.199997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-3.477859</v>
+        <v>-5.641028</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1175.25</v>
+        <v>1184.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>0.277304</v>
+        <v>1.066553</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7728.200195</v>
+        <v>7748.5</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>3.184097</v>
+        <v>3.455133</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>165.050003</v>
+        <v>164.669998</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-5.696492</v>
+        <v>-5.913613</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1612</v>
+        <v>5.189</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1.636436</v>
+        <v>2.183886</v>
       </c>
     </row>
     <row r="124">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>52485.03125</v>
+        <v>52208.058594</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>0.316962</v>
+        <v>-0.212428</v>
       </c>
     </row>
     <row r="184">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53770.269531</v>
+        <v>53839.988281</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.448771</v>
+        <v>3.12582</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9514</v>
+        <v>5.9962</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1.768943</v>
+        <v>2.535028</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>167491</v>
+        <v>167101</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-5.903404</v>
+        <v>-6.122506</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>450.350006</v>
+        <v>452.440002</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>5.126168</v>
+        <v>5.61404</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>478.25</v>
+        <v>476</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>8.508224999999999</v>
+        <v>7.997731</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26588.490234</v>
+        <v>26803.029297</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>4.786978</v>
+        <v>5.632491</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4450.399902</v>
+        <v>4407.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>9.910838999999999</v>
+        <v>8.861223000000001</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>87.220001</v>
+        <v>87.160004</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-3.217933</v>
+        <v>-3.284508</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>81.459999</v>
+        <v>81.699997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-3.791188</v>
+        <v>-3.507737</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>101.199997</v>
+        <v>100.769997</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-5.641028</v>
+        <v>-6.041961</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1184.5</v>
+        <v>1186.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>1.066553</v>
+        <v>1.237201</v>
       </c>
     </row>
     <row r="795">
@@ -56731,7 +56731,7 @@
         </is>
       </c>
       <c r="H854" t="n">
-        <v>7489.720215</v>
+        <v>7437.629883</v>
       </c>
       <c r="I854" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         </is>
       </c>
       <c r="N854" t="n">
-        <v>-0.12854</v>
+        <v>-0.823137</v>
       </c>
     </row>
     <row r="855">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7748.5</v>
+        <v>7798.990234</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>3.455133</v>
+        <v>4.858542</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>164.669998</v>
+        <v>164.149994</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-5.913613</v>
+        <v>-6.210725</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.189</v>
+        <v>5.2132</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.183886</v>
+        <v>2.660442</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53839.988281</v>
+        <v>53732.410156</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>3.12582</v>
+        <v>2.919763</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9962</v>
+        <v>6.0459</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2.535028</v>
+        <v>3.384894</v>
       </c>
     </row>
     <row r="246">
@@ -20515,7 +20515,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>177999</v>
+        <v>177159</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>3.473353</v>
+        <v>2.985049</v>
       </c>
     </row>
     <row r="306">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>167101</v>
+        <v>166934</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-6.122506</v>
+        <v>-5.771651</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>452.440002</v>
+        <v>457</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>5.61404</v>
+        <v>6.67849</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>7.997731</v>
+        <v>4.140669</v>
       </c>
     </row>
     <row r="429">
@@ -32587,7 +32587,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>25373.849609</v>
+        <v>25122.179688</v>
       </c>
       <c r="I488" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         </is>
       </c>
       <c r="N488" t="n">
-        <v>-3.203937</v>
+        <v>-4.164006</v>
       </c>
     </row>
     <row r="489">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26803.029297</v>
+        <v>26729.160156</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>5.632491</v>
+        <v>6.39666</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4407.899902</v>
+        <v>4380.399902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>8.861223000000001</v>
+        <v>8.18206</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>87.160004</v>
+        <v>88.519997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-3.284508</v>
+        <v>-1.775417</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>81.699997</v>
+        <v>82.400002</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-3.507737</v>
+        <v>-2.680993</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>100.769997</v>
+        <v>100.970001</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-6.041961</v>
+        <v>-5.855477</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1186.5</v>
+        <v>1173.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>1.237201</v>
+        <v>0.149317</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7798.990234</v>
+        <v>7785.759766</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>4.858542</v>
+        <v>4.680656</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>164.149994</v>
+        <v>163.899994</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-6.210725</v>
+        <v>-6.353565</v>
       </c>
     </row>
     <row r="63">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>52208.058594</v>
+        <v>52485.03125</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>-0.212428</v>
+        <v>0.316962</v>
       </c>
     </row>
     <row r="184">
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.919763</v>
+        <v>2.376637</v>
       </c>
     </row>
     <row r="185">
@@ -20515,7 +20515,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>177159</v>
+        <v>177999</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>2.985049</v>
+        <v>3.473353</v>
       </c>
     </row>
     <row r="306">
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-5.771651</v>
+        <v>-6.216327</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>457</v>
+        <v>458.100006</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>6.67849</v>
+        <v>6.935267</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>459</v>
+        <v>483.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>4.140669</v>
+        <v>9.642655</v>
       </c>
     </row>
     <row r="429">
@@ -32587,7 +32587,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>25122.179688</v>
+        <v>25373.849609</v>
       </c>
       <c r="I488" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         </is>
       </c>
       <c r="N488" t="n">
-        <v>-4.164006</v>
+        <v>-3.203937</v>
       </c>
     </row>
     <row r="489">
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>6.39666</v>
+        <v>5.341367</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4380.399902</v>
+        <v>4437.299805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>8.18206</v>
+        <v>9.587308</v>
       </c>
     </row>
     <row r="551">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>100.970001</v>
+        <v>100.120003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-5.855477</v>
+        <v>-6.648016</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1173.75</v>
+        <v>1192.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>0.149317</v>
+        <v>1.749147</v>
       </c>
     </row>
     <row r="795">
@@ -56731,7 +56731,7 @@
         </is>
       </c>
       <c r="H854" t="n">
-        <v>7437.629883</v>
+        <v>7489.720215</v>
       </c>
       <c r="I854" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         </is>
       </c>
       <c r="N854" t="n">
-        <v>-0.823137</v>
+        <v>-0.12854</v>
       </c>
     </row>
     <row r="855">
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>4.680656</v>
+        <v>3.952612</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.2132</v>
+        <v>5.2265</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.660442</v>
+        <v>2.922349</v>
       </c>
     </row>
     <row r="124">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.0459</v>
+        <v>6.0614</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>3.384894</v>
+        <v>3.649946</v>
       </c>
     </row>
     <row r="246">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>483.25</v>
+        <v>486</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>9.642655</v>
+        <v>10.266591</v>
       </c>
     </row>
     <row r="429">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4437.299805</v>
+        <v>4452.100098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>9.587308</v>
+        <v>9.952828999999999</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>88.519997</v>
+        <v>89.480003</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-1.775417</v>
+        <v>-0.710164</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>82.400002</v>
+        <v>83.050003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-2.680993</v>
+        <v>-1.913305</v>
       </c>
     </row>
     <row r="673">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1192.5</v>
+        <v>1198.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>1.749147</v>
+        <v>2.282423</v>
       </c>
     </row>
     <row r="795">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.2265</v>
+        <v>5.2</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.922349</v>
+        <v>2.400496</v>
       </c>
     </row>
     <row r="124">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.0614</v>
+        <v>6.0196</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>3.649946</v>
+        <v>2.935165</v>
       </c>
     </row>
     <row r="246">
@@ -20515,7 +20515,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>177999</v>
+        <v>177159</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>3.473353</v>
+        <v>2.985049</v>
       </c>
     </row>
     <row r="306">
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-6.216327</v>
+        <v>-5.771651</v>
       </c>
     </row>
     <row r="307">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>486</v>
+        <v>492.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>10.266591</v>
+        <v>11.798071</v>
       </c>
     </row>
     <row r="429">
@@ -32587,7 +32587,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>25373.849609</v>
+        <v>25122.179688</v>
       </c>
       <c r="I488" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         </is>
       </c>
       <c r="N488" t="n">
-        <v>-3.203937</v>
+        <v>-4.164006</v>
       </c>
     </row>
     <row r="489">
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>5.341367</v>
+        <v>6.39666</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4452.100098</v>
+        <v>4451.399902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>9.952828999999999</v>
+        <v>9.935536000000001</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>89.480003</v>
+        <v>91.129997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-0.710164</v>
+        <v>1.120722</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>83.050003</v>
+        <v>84.370003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-1.913305</v>
+        <v>-0.354311</v>
       </c>
     </row>
     <row r="673">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1198.75</v>
+        <v>1225</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.282423</v>
+        <v>4.522184</v>
       </c>
     </row>
     <row r="795">
@@ -56731,7 +56731,7 @@
         </is>
       </c>
       <c r="H854" t="n">
-        <v>7489.720215</v>
+        <v>7437.629883</v>
       </c>
       <c r="I854" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         </is>
       </c>
       <c r="N854" t="n">
-        <v>-0.12854</v>
+        <v>-0.823137</v>
       </c>
     </row>
     <row r="855">
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>3.952612</v>
+        <v>4.680656</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>163.899994</v>
+        <v>163.800003</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-6.353565</v>
+        <v>-6.410696</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.2</v>
+        <v>5.2196</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.400496</v>
+        <v>2.786475</v>
       </c>
     </row>
     <row r="124">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>52485.03125</v>
+        <v>52208.058594</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>0.316962</v>
+        <v>-0.212428</v>
       </c>
     </row>
     <row r="184">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53732.410156</v>
+        <v>53343.398438</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.376637</v>
+        <v>2.174645</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.0196</v>
+        <v>6.0607</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2.935165</v>
+        <v>3.637976</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>166934</v>
+        <v>166335</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-5.771651</v>
+        <v>-6.109766</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>458.100006</v>
+        <v>453.890015</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>6.935267</v>
+        <v>5.95252</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>492.75</v>
+        <v>490.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>11.798071</v>
+        <v>11.230856</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26729.160156</v>
+        <v>26289.710938</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>6.39666</v>
+        <v>4.647412</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4451.399902</v>
+        <v>4422.299805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>9.935536000000001</v>
+        <v>9.216856</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>91.129997</v>
+        <v>92.010002</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>1.120722</v>
+        <v>2.097203</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>84.370003</v>
+        <v>85.019997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-0.354311</v>
+        <v>0.413368</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>100.120003</v>
+        <v>100</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-6.648016</v>
+        <v>-6.759907</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1225</v>
+        <v>1227.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>4.522184</v>
+        <v>4.714164</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7785.759766</v>
+        <v>7691.759766</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>4.680656</v>
+        <v>3.416813</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>163.800003</v>
+        <v>163.550003</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-6.410696</v>
+        <v>-6.553537</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.2196</v>
+        <v>5.1681</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.786475</v>
+        <v>1.77231</v>
       </c>
     </row>
     <row r="124">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>52208.058594</v>
+        <v>52485.03125</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>-0.212428</v>
+        <v>0.316962</v>
       </c>
     </row>
     <row r="184">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53343.398438</v>
+        <v>53463.050781</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.174645</v>
+        <v>1.863426</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.0607</v>
+        <v>6.0502</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>3.637976</v>
+        <v>3.458426</v>
       </c>
     </row>
     <row r="246">
@@ -20515,7 +20515,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>177159</v>
+        <v>177999</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>2.985049</v>
+        <v>3.473353</v>
       </c>
     </row>
     <row r="306">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>166335</v>
+        <v>167830</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-6.109766</v>
+        <v>-5.712953</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>453.890015</v>
+        <v>453.25</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>5.95252</v>
+        <v>5.80312</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>490.25</v>
+        <v>502</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>11.230856</v>
+        <v>13.896767</v>
       </c>
     </row>
     <row r="429">
@@ -32587,7 +32587,7 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>25122.179688</v>
+        <v>25373.849609</v>
       </c>
       <c r="I488" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         </is>
       </c>
       <c r="N488" t="n">
-        <v>-4.164006</v>
+        <v>-3.203937</v>
       </c>
     </row>
     <row r="489">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26289.710938</v>
+        <v>26331.089844</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>4.647412</v>
+        <v>3.772546</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4422.299805</v>
+        <v>4543.5</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>9.216856</v>
+        <v>12.210118</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>92.010002</v>
+        <v>93.849998</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>2.097203</v>
+        <v>4.138921</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>85.019997</v>
+        <v>86.589996</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>0.413368</v>
+        <v>2.267625</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-6.759907</v>
+        <v>-7.692308</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1227.25</v>
+        <v>1241.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>4.714164</v>
+        <v>5.930034</v>
       </c>
     </row>
     <row r="795">
@@ -56731,7 +56731,7 @@
         </is>
       </c>
       <c r="H854" t="n">
-        <v>7437.629883</v>
+        <v>7489.720215</v>
       </c>
       <c r="I854" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         </is>
       </c>
       <c r="N854" t="n">
-        <v>-0.823137</v>
+        <v>-0.12854</v>
       </c>
     </row>
     <row r="855">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7691.759766</v>
+        <v>7707.97998</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>3.416813</v>
+        <v>2.914124</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>163.550003</v>
+        <v>165</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-6.553537</v>
+        <v>-5.725062</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1681</v>
+        <v>5.1931</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1.77231</v>
+        <v>2.264622</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53463.050781</v>
+        <v>52759.210938</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.863426</v>
+        <v>0.522396</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.0502</v>
+        <v>6.0795</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>3.458426</v>
+        <v>3.95946</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>167830</v>
+        <v>167927</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-5.712953</v>
+        <v>-5.658459</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>453.25</v>
+        <v>450.299988</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>5.80312</v>
+        <v>5.114492</v>
       </c>
     </row>
     <row r="368">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26331.089844</v>
+        <v>26067.169922</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>3.772546</v>
+        <v>2.732421</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4543.5</v>
+        <v>4640.700195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>12.210118</v>
+        <v>14.610656</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>93.849998</v>
+        <v>94.05999799999999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>4.138921</v>
+        <v>4.371943</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>86.589996</v>
+        <v>87.25</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>2.267625</v>
+        <v>3.047126</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>99</v>
+        <v>99.94000200000001</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-7.692308</v>
+        <v>-6.815849</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1241.5</v>
+        <v>1231.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>5.930034</v>
+        <v>5.098123</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7707.97998</v>
+        <v>7641.160156</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.914124</v>
+        <v>2.021971</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1931</v>
+        <v>5.1366</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.264622</v>
+        <v>1.152002</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>52759.210938</v>
+        <v>53277.011719</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.522396</v>
+        <v>1.508964</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.0795</v>
+        <v>6</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>3.95946</v>
+        <v>2.600007</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>167927</v>
+        <v>171031.734375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-5.658459</v>
+        <v>-3.914216</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>450.299988</v>
+        <v>448</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>5.114492</v>
+        <v>4.577601</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>502</v>
+        <v>483.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>13.896767</v>
+        <v>9.756098</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26067.169922</v>
+        <v>26180.460938</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>2.732421</v>
+        <v>3.178908</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4640.700195</v>
+        <v>4624.100098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>14.610656</v>
+        <v>14.200686</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>94.05999799999999</v>
+        <v>94.389999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>4.371943</v>
+        <v>4.738123</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>87.25</v>
+        <v>87.05999799999999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>3.047126</v>
+        <v>2.822723</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>99.94000200000001</v>
+        <v>99.25</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-6.815849</v>
+        <v>-7.459207</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1231.75</v>
+        <v>1225</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>5.098123</v>
+        <v>4.522184</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7641.160156</v>
+        <v>7674.370117</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.021971</v>
+        <v>2.465378</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1366</v>
+        <v>5.154</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1.152002</v>
+        <v>1.494646</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53277.011719</v>
+        <v>53417.160156</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.508964</v>
+        <v>1.77599</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9925</v>
+        <v>6.0109</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2.471754</v>
+        <v>2.786397</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>170448.875</v>
+        <v>171907</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-4.241667</v>
+        <v>-3.422491</v>
       </c>
     </row>
     <row r="307">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>522.5</v>
+        <v>514.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>18.54793</v>
+        <v>16.67612</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26180.460938</v>
+        <v>25980.189453</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>3.178908</v>
+        <v>2.389625</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4700.799805</v>
+        <v>4693.100098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>16.094927</v>
+        <v>15.904769</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>92.779999</v>
+        <v>88.019997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>2.951616</v>
+        <v>-2.330233</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>85.040001</v>
+        <v>82.540001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>0.436994</v>
+        <v>-2.515646</v>
       </c>
     </row>
     <row r="673">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1237.25</v>
+        <v>1218.25</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>5.567406</v>
+        <v>3.946246</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7674.370117</v>
+        <v>7652.859863</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.465378</v>
+        <v>2.178181</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>168.330002</v>
+        <v>169.009995</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-3.822422</v>
+        <v>-3.433899</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.154</v>
+        <v>5.148</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1.494646</v>
+        <v>1.37649</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53417.160156</v>
+        <v>53577.398438</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.77599</v>
+        <v>2.081293</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.0109</v>
+        <v>6.0044</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2.786397</v>
+        <v>2.675243</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>171907</v>
+        <v>174577</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-3.422491</v>
+        <v>-1.922483</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>445.850006</v>
+        <v>444.700012</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>4.075723</v>
+        <v>3.807278</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>514.25</v>
+        <v>528</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>16.67612</v>
+        <v>19.795803</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>25980.189453</v>
+        <v>26151.300781</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>2.389625</v>
+        <v>3.063986</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4693.100098</v>
+        <v>4670.700195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>15.904769</v>
+        <v>15.351562</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>88.019997</v>
+        <v>84.910004</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-2.330233</v>
+        <v>-5.781179</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>82.540001</v>
+        <v>80.139999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-2.515646</v>
+        <v>-5.350182</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>102.25</v>
+        <v>102.639999</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-4.662005</v>
+        <v>-4.298369</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1218.25</v>
+        <v>1240.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>3.946246</v>
+        <v>5.866041</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7652.859863</v>
+        <v>7677.279785</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.178181</v>
+        <v>2.504227</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>169.009995</v>
+        <v>172.399994</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-3.433899</v>
+        <v>-1.496978</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.148</v>
+        <v>5.1611</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1.37649</v>
+        <v>1.634464</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53577.398438</v>
+        <v>53569.441406</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.081293</v>
+        <v>2.066132</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.0044</v>
+        <v>6.013</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2.675243</v>
+        <v>2.822307</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>174577</v>
+        <v>175329.453125</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-1.922483</v>
+        <v>-1.499754</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>444.700012</v>
+        <v>450.690002</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>3.807278</v>
+        <v>5.205534</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>528</v>
+        <v>531.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>19.795803</v>
+        <v>20.589904</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26151.300781</v>
+        <v>26541.351562</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>3.063986</v>
+        <v>4.601202</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4670.700195</v>
+        <v>4660.600098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>15.351562</v>
+        <v>15.102121</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>84.910004</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-5.781179</v>
+        <v>-1.719932</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>80.139999</v>
+        <v>83.639999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-5.350182</v>
+        <v>-1.216486</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>102.639999</v>
+        <v>105.360001</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-4.298369</v>
+        <v>-1.762237</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1240.75</v>
+        <v>1263.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>5.866041</v>
+        <v>7.807167</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7677.279785</v>
+        <v>7730.990234</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.504227</v>
+        <v>3.221349</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>172.399994</v>
+        <v>172.720001</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-1.496978</v>
+        <v>-1.314137</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1611</v>
+        <v>5.1925</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1.634464</v>
+        <v>2.252809</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53569.441406</v>
+        <v>53559.988281</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.066132</v>
+        <v>2.048121</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.013</v>
+        <v>6.0137</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2.822307</v>
+        <v>2.834277</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>175329.453125</v>
+        <v>175664.625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-1.499754</v>
+        <v>-1.311454</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>450.690002</v>
+        <v>452.049988</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>5.205534</v>
+        <v>5.522998</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>531.5</v>
+        <v>536.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>20.589904</v>
+        <v>21.667612</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26541.351562</v>
+        <v>26402.423828</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>4.601202</v>
+        <v>4.053678</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4660.600098</v>
+        <v>4505.799805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>15.102121</v>
+        <v>11.279042</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>88.56999999999999</v>
+        <v>88.230003</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-1.719932</v>
+        <v>-2.097203</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>83.639999</v>
+        <v>83.400002</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-1.216486</v>
+        <v>-1.499937</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>105.360001</v>
+        <v>104.580002</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-1.762237</v>
+        <v>-2.489509</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1263.5</v>
+        <v>1287.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>7.807167</v>
+        <v>9.87628</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7730.990234</v>
+        <v>7711.759766</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>3.221349</v>
+        <v>2.964591</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>172.720001</v>
+        <v>172.399994</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-1.314137</v>
+        <v>-1.496978</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1925</v>
+        <v>5.2054</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.252809</v>
+        <v>2.506839</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53559.988281</v>
+        <v>53569.441406</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.048121</v>
+        <v>2.066132</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.0137</v>
+        <v>6.0054</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2.834277</v>
+        <v>2.69235</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>175664.625</v>
+        <v>175135</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-1.311454</v>
+        <v>-1.608998</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>452.049988</v>
+        <v>450</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>5.522998</v>
+        <v>5.044465</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>536.25</v>
+        <v>510.25</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>21.667612</v>
+        <v>15.768576</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26402.423828</v>
+        <v>26541.349609</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>4.053678</v>
+        <v>4.601194</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4505.799805</v>
+        <v>4609.700195</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>11.279042</v>
+        <v>13.845054</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>88.230003</v>
+        <v>89.699997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-2.097203</v>
+        <v>-0.466052</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>83.400002</v>
+        <v>83.529999</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-1.499937</v>
+        <v>-1.346403</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>104.580002</v>
+        <v>105.169998</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-2.489509</v>
+        <v>-1.939396</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1287.75</v>
+        <v>1256.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>9.87628</v>
+        <v>7.209898</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7711.759766</v>
+        <v>7730.990234</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.964591</v>
+        <v>3.221349</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.2054</v>
+        <v>5.185</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.506839</v>
+        <v>2.105113</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53569.441406</v>
+        <v>53559.988281</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.066132</v>
+        <v>2.048121</v>
       </c>
     </row>
     <row r="185">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>175135</v>
+        <v>175665</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-1.608998</v>
+        <v>-1.311243</v>
       </c>
     </row>
     <row r="307">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>510.25</v>
+        <v>536.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>15.768576</v>
+        <v>21.724334</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26541.349609</v>
+        <v>26402.419922</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>4.601194</v>
+        <v>4.053663</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4609.700195</v>
+        <v>4529.899902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>13.845054</v>
+        <v>11.874239</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>89.699997</v>
+        <v>88.099998</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-0.466052</v>
+        <v>-2.241461</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>83.529999</v>
+        <v>83.400002</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-1.346403</v>
+        <v>-1.499937</v>
       </c>
     </row>
     <row r="673">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1256.5</v>
+        <v>1288</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>7.209898</v>
+        <v>9.897610999999999</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7730.990234</v>
+        <v>7711.759766</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>3.221349</v>
+        <v>2.964591</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>172.399994</v>
+        <v>174.800003</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>-1.496978</v>
+        <v>-0.125701</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.185</v>
+        <v>5.1834</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2.105113</v>
+        <v>2.073609</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53559.988281</v>
+        <v>53199.460938</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>2.048121</v>
+        <v>1.361207</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.0054</v>
+        <v>6.0184</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2.69235</v>
+        <v>2.91465</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>175665</v>
+        <v>177580.765625</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>-1.311243</v>
+        <v>-0.234964</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>450</v>
+        <v>449.230011</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>5.044465</v>
+        <v>4.864725</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>536.5</v>
+        <v>538</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>21.724334</v>
+        <v>22.064663</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26402.419922</v>
+        <v>26289.875</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>4.053663</v>
+        <v>3.610116</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4529.899902</v>
+        <v>4483.399902</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>11.874239</v>
+        <v>10.725835</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>88.099998</v>
+        <v>88.269997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>-2.241461</v>
+        <v>-2.052825</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>83.400002</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>-1.499937</v>
+        <v>1.192869</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>105.169998</v>
+        <v>106.550003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>-1.939396</v>
+        <v>-0.652678</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>9.897610999999999</v>
+        <v>10.068259</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7711.759766</v>
+        <v>7672.839844</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>2.964591</v>
+        <v>2.444946</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>172.720001</v>
+        <v>174.779999</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>-1.314137</v>
+        <v>-0.13713</v>
       </c>
     </row>
     <row r="62">
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>177.610001</v>
+        <v>180.369995</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.831171</v>
+        <v>3.198304</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1434</v>
+        <v>5.1304</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-0.920781</v>
+        <v>-1.171205</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53141.730469</v>
+        <v>53092.410156</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-0.08304499999999999</v>
+        <v>-0.175776</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9697</v>
+        <v>5.9502</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.664187</v>
+        <v>-0.988663</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>180393.8125</v>
+        <v>183242.234375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>1.676716</v>
+        <v>3.282193</v>
       </c>
     </row>
     <row r="307">
@@ -24539,7 +24539,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>452.049988</v>
+        <v>449.350006</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>5.522998</v>
+        <v>4.892736</v>
       </c>
     </row>
     <row r="367">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>444.790009</v>
+        <v>442.920013</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.606012</v>
+        <v>-1.430954</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>542.25</v>
+        <v>541</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>5.291262</v>
+        <v>5.048544</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26179.060547</v>
+        <v>26157.546875</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-0.727431</v>
+        <v>-0.809012</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4419.100098</v>
+        <v>4431.299805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.270813</v>
+        <v>0.004507</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>92.06999999999999</v>
+        <v>93.889999</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>1.746051</v>
+        <v>3.757323</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>87.650002</v>
+        <v>89.129997</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>2.203824</v>
+        <v>3.929565</v>
       </c>
     </row>
     <row r="673">
@@ -48683,7 +48683,7 @@
         </is>
       </c>
       <c r="H732" t="n">
-        <v>104.580002</v>
+        <v>106.129997</v>
       </c>
       <c r="I732" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         </is>
       </c>
       <c r="N732" t="n">
-        <v>-2.489509</v>
+        <v>-1.044292</v>
       </c>
     </row>
     <row r="733">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>108.040001</v>
+        <v>109.370003</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>3.308471</v>
+        <v>3.052865</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.881788</v>
+        <v>2.25446</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7659.640137</v>
+        <v>7656.77002</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.344776</v>
+        <v>-0.382118</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>180.369995</v>
+        <v>184.940002</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.198304</v>
+        <v>5.813024</v>
       </c>
     </row>
     <row r="63">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.1304</v>
+        <v>5.0978</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>-1.171205</v>
+        <v>-1.799199</v>
       </c>
     </row>
     <row r="124">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>53092.410156</v>
+        <v>53321.730469</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>-0.175776</v>
+        <v>0.255391</v>
       </c>
     </row>
     <row r="185">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>5.9502</v>
+        <v>5.9255</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>-0.988663</v>
+        <v>-1.399674</v>
       </c>
     </row>
     <row r="246">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>183242.234375</v>
+        <v>187884.234375</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>3.282193</v>
+        <v>5.898598</v>
       </c>
     </row>
     <row r="307">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>442.920013</v>
+        <v>444.200012</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-1.430954</v>
+        <v>-1.146099</v>
       </c>
     </row>
     <row r="368">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>5.048544</v>
+        <v>2.330097</v>
       </c>
     </row>
     <row r="429">
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>26157.546875</v>
+        <v>26400.578125</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>-0.809012</v>
+        <v>0.112577</v>
       </c>
     </row>
     <row r="490">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4431.299805</v>
+        <v>4514.799805</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>0.004507</v>
+        <v>1.888915</v>
       </c>
     </row>
     <row r="551">
@@ -40701,7 +40701,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>93.889999</v>
+        <v>96.199997</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         </is>
       </c>
       <c r="N611" t="n">
-        <v>3.757323</v>
+        <v>6.310089</v>
       </c>
     </row>
     <row r="612">
@@ -44725,7 +44725,7 @@
         </is>
       </c>
       <c r="H672" t="n">
-        <v>89.129997</v>
+        <v>91.870003</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="N672" t="n">
-        <v>3.929565</v>
+        <v>7.124534</v>
       </c>
     </row>
     <row r="673">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>109.370003</v>
+        <v>112.779999</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>3.052865</v>
+        <v>6.265902</v>
       </c>
     </row>
     <row r="734">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1304</v>
+        <v>1292.5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>2.25446</v>
+        <v>1.352676</v>
       </c>
     </row>
     <row r="795">
@@ -56797,7 +56797,7 @@
         </is>
       </c>
       <c r="H855" t="n">
-        <v>7656.77002</v>
+        <v>7696.549805</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="N855" t="n">
-        <v>-0.382118</v>
+        <v>0.135434</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>182.25</v>
+        <v>181.940002</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4.273945</v>
+        <v>4.096581</v>
       </c>
     </row>
     <row r="63">
@@ -24605,7 +24605,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>446</v>
+        <v>447.350006</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>-0.745523</v>
+        <v>-0.445087</v>
       </c>
     </row>
     <row r="368">
@@ -48749,7 +48749,7 @@
         </is>
       </c>
       <c r="H733" t="n">
-        <v>111.059998</v>
+        <v>110.989998</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>4.645247</v>
+        <v>4.57929</v>
       </c>
     </row>
     <row r="734">

--- a/data/final/yahoo/base_yahoo_mensal_longa.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_longa.xlsx
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>512</v>
+        <v>536.75</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>-0.582524</v>
+        <v>4.223301</v>
       </c>
     </row>
     <row r="429">
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>4429.799805</v>
+        <v>4476.600098</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>-0.029345</v>
+        <v>1.026833</v>
       </c>
     </row>
     <row r="551">
@@ -52773,7 +52773,7 @@
         </is>
       </c>
       <c r="H794" t="n">
-        <v>1293.75</v>
+        <v>1309.75</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>1.450696</v>
+        <v>2.705352</v>
       </c>
     </row>
     <row r="795">
